--- a/data/fsa/2026_MYA.xlsx
+++ b/data/fsa/2026_MYA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-0911\Program Year 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2026-1009\Program Year 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DA8B915-F945-4169-B093-37A46E7DE1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B30B39A-A114-4A7E-B939-4F909FA48568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
     <t>TABLE 1. 2020/21-2026/27 MARKET YEAR AVERAGE (MYA) PRICES</t>
   </si>
   <si>
-    <t>September 11, 2026 1/</t>
+    <t>October 9, 2026 1/</t>
   </si>
   <si>
     <t>Commodity</t>
@@ -691,7 +691,7 @@
         <v>17</v>
       </c>
       <c r="L5" s="6">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>18</v>
@@ -849,13 +849,13 @@
         <v>4.24</v>
       </c>
       <c r="J9" s="5">
-        <v>4.1500000000000004</v>
+        <v>4.16</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L9" s="6">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>18</v>
@@ -890,13 +890,13 @@
         <v>4.07</v>
       </c>
       <c r="J10" s="5">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L10" s="6">
-        <v>4.5999999999999996</v>
+        <v>4.5</v>
       </c>
       <c r="M10" s="7" t="s">
         <v>18</v>
@@ -934,7 +934,7 @@
         <v>10.5</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L11" s="6">
         <v>12</v>
@@ -978,7 +978,7 @@
         <v>17</v>
       </c>
       <c r="L12" s="9">
-        <v>0.112</v>
+        <v>9.4E-2</v>
       </c>
       <c r="M12" s="7" t="s">
         <v>18</v>
@@ -1019,7 +1019,7 @@
         <v>17</v>
       </c>
       <c r="L13" s="9">
-        <v>0.17</v>
+        <v>0.16900000000000001</v>
       </c>
       <c r="M13" s="7" t="s">
         <v>18</v>
@@ -1060,7 +1060,7 @@
         <v>17</v>
       </c>
       <c r="L14" s="9">
-        <v>0.245</v>
+        <v>0.26500000000000001</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>18</v>
@@ -1095,13 +1095,13 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="J15" s="8">
-        <v>0.254</v>
+        <v>0.25600000000000001</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L15" s="9">
-        <v>0.21</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="M15" s="7" t="s">
         <v>18</v>
@@ -1139,10 +1139,10 @@
         <v>0.16400000000000001</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L16" s="9">
-        <v>0.16700000000000001</v>
+        <v>0.16800000000000001</v>
       </c>
       <c r="M16" s="7" t="s">
         <v>18</v>
@@ -1177,13 +1177,13 @@
         <v>0.23799999999999999</v>
       </c>
       <c r="J17" s="8">
-        <v>0.23499999999999999</v>
+        <v>0.24199999999999999</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L17" s="9">
-        <v>0.247</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>18</v>
@@ -1224,7 +1224,7 @@
         <v>17</v>
       </c>
       <c r="L18" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>18</v>
@@ -1259,13 +1259,13 @@
         <v>0.44900000000000001</v>
       </c>
       <c r="J19" s="8">
-        <v>0.3075</v>
+        <v>0.309</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L19" s="9">
-        <v>0.317</v>
+        <v>0.33400000000000002</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>18</v>
@@ -1341,13 +1341,13 @@
         <v>0.24299999999999999</v>
       </c>
       <c r="J21" s="8">
-        <v>0.20799999999999999</v>
+        <v>0.20399999999999999</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L21" s="9">
-        <v>0.215</v>
+        <v>0.22750000000000001</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>18</v>
@@ -1385,7 +1385,7 @@
         <v>0.32</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L22" s="9">
         <v>0.36599999999999999</v>
@@ -1423,10 +1423,10 @@
         <v>0.54</v>
       </c>
       <c r="J23" s="8">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L23" s="9">
         <v>0.38</v>
@@ -1464,13 +1464,13 @@
         <v>0.34039999999999998</v>
       </c>
       <c r="J24" s="8">
-        <v>0.34110000000000001</v>
+        <v>0.34079999999999999</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L24" s="9">
-        <v>0.41139999999999999</v>
+        <v>0.41470000000000001</v>
       </c>
       <c r="M24" s="7" t="s">
         <v>18</v>
@@ -1511,7 +1511,7 @@
         <v>18</v>
       </c>
       <c r="L25" s="9">
-        <v>0.13500000000000001</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="M25" s="7" t="s">
         <v>18</v>
@@ -1679,6 +1679,6 @@
     <mergeCell ref="A31:M31"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="1.6" header="0" footer="0"/>
-  <pageSetup scale="88" orientation="landscape" cellComments="atEnd" horizontalDpi="2400" verticalDpi="2400" r:id="rId1"/>
+  <pageSetup scale="88" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>